--- a/ChainLadderFinal.xlsx
+++ b/ChainLadderFinal.xlsx
@@ -8,14 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My PC (DESKTOP-JQBDP5S)\Downloads\ChainLadder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{653062DD-68B9-404A-95D8-9EB19F20AAC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90F688C5-51CF-4F32-B441-0987B4B50120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57600" yWindow="16035" windowWidth="13860" windowHeight="16200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="15915" windowWidth="27960" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
-    <sheet name="Actuarial Triangle" sheetId="2" r:id="rId2"/>
+    <sheet name="Dashboard-Lists" sheetId="3" state="hidden" r:id="rId2"/>
+    <sheet name="Actuarial Triangle" sheetId="2" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="Modifier">Table4[[#Headers],[Modifier]]</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -34,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="43">
   <si>
     <t>State Farm Cumulative Loss Triangle</t>
   </si>
@@ -72,9 +76,6 @@
     <t>50 to 72</t>
   </si>
   <si>
-    <t>Executive Loss Reserve Summary</t>
-  </si>
-  <si>
     <t>Passenger Auto</t>
   </si>
   <si>
@@ -84,9 +85,6 @@
     <t>Evaluation Date:</t>
   </si>
   <si>
-    <t>Model indicated LDF</t>
-  </si>
-  <si>
     <t>Total Cumulative Paid-To-Date</t>
   </si>
   <si>
@@ -96,10 +94,79 @@
     <t>CDF</t>
   </si>
   <si>
-    <t>Projected Ulimate Loss</t>
-  </si>
-  <si>
     <t>Industry Cumulative Loss Triangle</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>Model Indicated LDF</t>
+  </si>
+  <si>
+    <t>Future Cost Predictor</t>
+  </si>
+  <si>
+    <t>Executive Loss Reserve Summary of State Farm</t>
+  </si>
+  <si>
+    <t>Executive Loss Summary of Industry</t>
+  </si>
+  <si>
+    <t>Current Year</t>
+  </si>
+  <si>
+    <t>Current Amount</t>
+  </si>
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>Calculation</t>
+  </si>
+  <si>
+    <t>Years</t>
+  </si>
+  <si>
+    <t>Models</t>
+  </si>
+  <si>
+    <t>Industry</t>
+  </si>
+  <si>
+    <t>Projected Ultimate Loss</t>
+  </si>
+  <si>
+    <t>Modifier</t>
+  </si>
+  <si>
+    <t>State Farm</t>
   </si>
 </sst>
 </file>
@@ -108,9 +175,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="m/d/yy;@"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -125,16 +192,36 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -142,25 +229,147 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -171,6 +380,178 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{192917D9-2D23-46EE-A110-D5B3064D2C72}" name="Table3" displayName="Table3" ref="A3:M13" totalsRowShown="0">
+  <autoFilter ref="A3:M13" xr:uid="{192917D9-2D23-46EE-A110-D5B3064D2C72}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+    <filterColumn colId="6" hiddenButton="1"/>
+    <filterColumn colId="7" hiddenButton="1"/>
+    <filterColumn colId="8" hiddenButton="1"/>
+    <filterColumn colId="9" hiddenButton="1"/>
+    <filterColumn colId="10" hiddenButton="1"/>
+    <filterColumn colId="11" hiddenButton="1"/>
+    <filterColumn colId="12" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{E73652C9-C63D-438D-B158-50F71E44BEC1}" name="State Farm Cumulative Loss Triangle" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{E8C9FFEE-D126-4C2D-BF9B-DDB6C0F8481A}" name="12"/>
+    <tableColumn id="3" xr3:uid="{F1B9EA65-6C9B-4A0B-89D5-82241C0E508D}" name="24"/>
+    <tableColumn id="4" xr3:uid="{B7D70EEB-5B23-406F-A95C-4739360E9268}" name="36"/>
+    <tableColumn id="5" xr3:uid="{FDFF45DF-4104-48D1-8156-7E4DCF4BDC0A}" name="48"/>
+    <tableColumn id="6" xr3:uid="{1B68D4DC-1C1A-4D13-B91B-5AFEC120DCAC}" name="60"/>
+    <tableColumn id="7" xr3:uid="{FBA4F111-9EC9-4049-8AC9-E1065CD1BC41}" name="72"/>
+    <tableColumn id="8" xr3:uid="{D570E26E-8D43-4B47-865E-8E2D8648057C}" name="84"/>
+    <tableColumn id="9" xr3:uid="{CB66E9EC-173E-4DD6-B9EE-7158A3805685}" name="96"/>
+    <tableColumn id="10" xr3:uid="{B575B536-DEE4-4E6C-B621-662357B31620}" name="108"/>
+    <tableColumn id="11" xr3:uid="{83B3F591-2371-4F17-9291-0E5E468833DB}" name="120"/>
+    <tableColumn id="12" xr3:uid="{C9060955-3DA9-469D-9CCA-CBCF1770E45C}" name="CDF"/>
+    <tableColumn id="13" xr3:uid="{7A1BCA85-EE56-4ACD-8445-BBDF02605EAB}" name="Projected Ultimate Loss"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FCDC1029-CAF8-45F4-A473-89939CD43320}" name="Table4" displayName="Table4" ref="A16:K18" totalsRowShown="0">
+  <autoFilter ref="A16:K18" xr:uid="{FCDC1029-CAF8-45F4-A473-89939CD43320}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+    <filterColumn colId="6" hiddenButton="1"/>
+    <filterColumn colId="7" hiddenButton="1"/>
+    <filterColumn colId="8" hiddenButton="1"/>
+    <filterColumn colId="9" hiddenButton="1"/>
+    <filterColumn colId="10" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{133180F1-39DA-4EB8-90B2-7FA0354FA756}" name="Maturity Interval"/>
+    <tableColumn id="2" xr3:uid="{BFB62A60-B1DA-446E-8F15-D1F1AB7B339E}" name="12 to 24" dataDxfId="1">
+      <calculatedColumnFormula>SUM(C4:C12)/SUM(B4:B12)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{FC2F138F-6423-4EA1-A19C-BE05CFDE6FDA}" name="24 to 36">
+      <calculatedColumnFormula>C16</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{5DDBE8A3-599C-431E-8F59-26F4FE376C54}" name="36 to 48">
+      <calculatedColumnFormula>D16</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{63FC4ADC-E84C-48CD-AF4E-0DA1DDD269E1}" name="48 to 60">
+      <calculatedColumnFormula>E16</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{BC05D953-6C2D-47EA-8D3A-33D226D02AD0}" name="50 to 72">
+      <calculatedColumnFormula>F16</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{0E5E13F9-7F2B-4CB9-BC8B-89107AA74F88}" name="72 to 84">
+      <calculatedColumnFormula>G16</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{E7B9A86A-DB53-4F2A-B05C-55CCD2D633FE}" name="84 to 96">
+      <calculatedColumnFormula>H16</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{278221C0-2037-44AA-9C4C-DF9E9FF33361}" name="96 to 108">
+      <calculatedColumnFormula>I16</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{297AE622-DAFA-4A51-A2A8-E880C79C50CA}" name="108 to 120">
+      <calculatedColumnFormula>J16</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="11" xr3:uid="{73DAC59B-C8DF-4189-A58C-78DF3942BD1F}" name="Modifier"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{0E2CCD21-394D-4884-B0C9-5BF7C6C11ECE}" name="Table9" displayName="Table9" ref="A23:M33" totalsRowShown="0">
+  <autoFilter ref="A23:M33" xr:uid="{0E2CCD21-394D-4884-B0C9-5BF7C6C11ECE}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+    <filterColumn colId="6" hiddenButton="1"/>
+    <filterColumn colId="7" hiddenButton="1"/>
+    <filterColumn colId="8" hiddenButton="1"/>
+    <filterColumn colId="9" hiddenButton="1"/>
+    <filterColumn colId="10" hiddenButton="1"/>
+    <filterColumn colId="11" hiddenButton="1"/>
+    <filterColumn colId="12" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{3602F9F5-7EA2-4692-B477-0065AE0DB844}" name="Industry Cumulative Loss Triangle" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{D2E2DD65-691A-4DF8-A3C8-E09CE7373FBB}" name="12"/>
+    <tableColumn id="3" xr3:uid="{0C2C2726-DFAF-4F7E-963D-BFE17CF3979F}" name="24"/>
+    <tableColumn id="4" xr3:uid="{3AF005E5-10F2-4200-925B-5304EE38B35F}" name="36"/>
+    <tableColumn id="5" xr3:uid="{65DC9FAC-3C0F-4EF4-ACEF-B5748EC4EFC6}" name="48"/>
+    <tableColumn id="6" xr3:uid="{CAC404C7-18F1-4831-8A34-D5A0FAD63680}" name="60"/>
+    <tableColumn id="7" xr3:uid="{071836D9-36B6-460B-9367-721AD127C66C}" name="72"/>
+    <tableColumn id="8" xr3:uid="{CAC90AF8-4D11-4B6B-A3D1-14838A11BC73}" name="84"/>
+    <tableColumn id="9" xr3:uid="{FDFA5DE4-68A6-41E0-BEF1-08321AD2CB67}" name="96"/>
+    <tableColumn id="10" xr3:uid="{0C55026E-F058-4D97-BFA3-FC04CB9886F0}" name="108"/>
+    <tableColumn id="11" xr3:uid="{1584C54C-6B54-46E4-830F-12AAF2998F39}" name="120"/>
+    <tableColumn id="12" xr3:uid="{E5A959D1-205A-4BF8-96BB-F2FF90EDE09C}" name="CDF"/>
+    <tableColumn id="13" xr3:uid="{E001D459-1B31-460D-BAA7-A54E088ED966}" name="Projected Ultimate Loss"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{E9C9E15E-F828-4265-AD7F-76FDE14F1A2D}" name="Table10" displayName="Table10" ref="A36:K38" totalsRowShown="0">
+  <autoFilter ref="A36:K38" xr:uid="{E9C9E15E-F828-4265-AD7F-76FDE14F1A2D}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
+    <filterColumn colId="4" hiddenButton="1"/>
+    <filterColumn colId="5" hiddenButton="1"/>
+    <filterColumn colId="6" hiddenButton="1"/>
+    <filterColumn colId="7" hiddenButton="1"/>
+    <filterColumn colId="8" hiddenButton="1"/>
+    <filterColumn colId="9" hiddenButton="1"/>
+    <filterColumn colId="10" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{1A934B4A-71B9-4C2C-A7AC-7C3089365560}" name="Maturity Interval"/>
+    <tableColumn id="2" xr3:uid="{828A49A4-66F7-42FF-82D2-A0204DD670EF}" name="12 to 24">
+      <calculatedColumnFormula>B36 * (1+ Modfier)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{55515840-C7B3-4DC7-A97D-99BAF55F8832}" name="24 to 36">
+      <calculatedColumnFormula>C36 * (1+ Modfier)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{BA6F72BB-A49C-46BA-A874-FC489F396571}" name="36 to 48">
+      <calculatedColumnFormula>D36 * (1+ Modfier)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{B5029975-5658-4FDE-8009-7465BACB092B}" name="48 to 60">
+      <calculatedColumnFormula>E36 * (1+ Modfier)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{C1423416-BAD9-46D1-AA76-6A9AFF277207}" name="50 to 72">
+      <calculatedColumnFormula>F36 * (1+ Modfier)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{84BDFD8E-D2ED-4029-AD5C-456D0063F85D}" name="72 to 84">
+      <calculatedColumnFormula>G36 * (1+ Modfier)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{4EFD49D9-0D54-4F71-B22A-B31A5243F25C}" name="84 to 96">
+      <calculatedColumnFormula>H36 * (1+ Modfier)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" xr3:uid="{6B92626E-B04F-4770-A226-44D3AB148F80}" name="96 to 108">
+      <calculatedColumnFormula>I36 * (1+ Modfier)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{32966693-F15A-4B95-8165-CAA49E61A059}" name="108 to 120">
+      <calculatedColumnFormula>J36 * (1+ Modfier)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="11" xr3:uid="{6FB1B461-46AC-46FC-B3BD-FD1FBCF7ADCC}" name="Modifier"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -458,121 +839,304 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.26953125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.36328125" customWidth="1"/>
-    <col min="3" max="3" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.1796875" customWidth="1"/>
     <col min="4" max="4" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.90625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="F1" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="18"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="F2" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="3">
+        <v>35795</v>
+      </c>
+      <c r="F3" s="11">
+        <v>14323</v>
+      </c>
+      <c r="G3" s="12">
+        <v>33239</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="I3" s="13">
+        <v>0.05</v>
+      </c>
+      <c r="J3" s="11">
+        <f>IF(NOT(OR( F3 = "", G3 = "", H3 = "", I3 = "")), IF(H3  = 'Dashboard-Lists'!E3, _xlfn.XLOOKUP(G3, Table3[State Farm Cumulative Loss Triangle], Table3[CDF]) * F3 * (1+ I3), _xlfn.XLOOKUP(G3, Table9[Industry Cumulative Loss Triangle], Table9[CDF])* F3* (1+I3)), "")</f>
+        <v>15172.291639592164</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="4">
+        <f>'Actuarial Triangle'!K3+ 'Actuarial Triangle'!J4 + 'Actuarial Triangle'!I5 +'Actuarial Triangle'!H6+'Actuarial Triangle'!G7+'Actuarial Triangle'!F8+'Actuarial Triangle'!E9+'Actuarial Triangle'!D10+'Actuarial Triangle'!C11+'Actuarial Triangle'!B12</f>
+        <v>69719804</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="4">
+        <f>SUM('Actuarial Triangle'!M2:M11)</f>
+        <v>70961158.729244575</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B6" s="1"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="17"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" s="6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="B10" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="3">
+        <v>35795</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="3">
-        <v>35795</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="4">
-        <f>SUM('Actuarial Triangle'!B4:K13)</f>
-        <v>373872882</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7">
-        <f>SUM('Actuarial Triangle'!M4:M13)</f>
-        <v>92385689.363382623</v>
-      </c>
+      <c r="B12" s="4">
+        <f>'Actuarial Triangle'!K23+'Actuarial Triangle'!J24+'Actuarial Triangle'!I25+'Actuarial Triangle'!H26+'Actuarial Triangle'!G27+'Actuarial Triangle'!F28+'Actuarial Triangle'!E29+'Actuarial Triangle'!D30+'Actuarial Triangle'!C31+'Actuarial Triangle'!B32</f>
+        <v>90371614</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="4">
+        <f>SUM('Actuarial Triangle'!M23:M32)</f>
+        <v>106235289.67720096</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B14" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="F1:J1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{789FFEFC-C9FD-49AE-BA3B-399FCF0690B8}">
+          <x14:formula1>
+            <xm:f>'Dashboard-Lists'!$D$3:$D$12</xm:f>
+          </x14:formula1>
+          <xm:sqref>G3</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{AEE8EDC2-B114-4828-92EC-F4841B1EF49E}">
+          <x14:formula1>
+            <xm:f>'Dashboard-Lists'!$E$3:$E$4</xm:f>
+          </x14:formula1>
+          <xm:sqref>H3</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:M20"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F60E1A28-235E-44CB-BF56-76975DF37D3E}">
+  <dimension ref="D2:E12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="31.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="4:5" x14ac:dyDescent="0.35">
+      <c r="D2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="4:5" x14ac:dyDescent="0.35">
+      <c r="D3" s="8">
+        <v>32143</v>
+      </c>
+      <c r="E3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="4:5" x14ac:dyDescent="0.35">
+      <c r="D4" s="8">
+        <v>32509</v>
+      </c>
+      <c r="E4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="4:5" x14ac:dyDescent="0.35">
+      <c r="D5" s="8">
+        <v>32874</v>
+      </c>
+    </row>
+    <row r="6" spans="4:5" x14ac:dyDescent="0.35">
+      <c r="D6" s="8">
+        <v>33239</v>
+      </c>
+    </row>
+    <row r="7" spans="4:5" x14ac:dyDescent="0.35">
+      <c r="D7" s="8">
+        <v>33604</v>
+      </c>
+    </row>
+    <row r="8" spans="4:5" x14ac:dyDescent="0.35">
+      <c r="D8" s="8">
+        <v>33970</v>
+      </c>
+    </row>
+    <row r="9" spans="4:5" x14ac:dyDescent="0.35">
+      <c r="D9" s="8">
+        <v>34335</v>
+      </c>
+    </row>
+    <row r="10" spans="4:5" x14ac:dyDescent="0.35">
+      <c r="D10" s="8">
+        <v>34700</v>
+      </c>
+    </row>
+    <row r="11" spans="4:5" x14ac:dyDescent="0.35">
+      <c r="D11" s="8">
+        <v>35065</v>
+      </c>
+    </row>
+    <row r="12" spans="4:5" x14ac:dyDescent="0.35">
+      <c r="D12" s="9">
+        <v>35431</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A3:M38"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="34.54296875" customWidth="1"/>
     <col min="2" max="2" width="18.36328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="21.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="10.36328125" customWidth="1"/>
+    <col min="10" max="11" width="11.453125" customWidth="1"/>
+    <col min="13" max="13" width="23.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="B3">
-        <v>12</v>
-      </c>
-      <c r="C3">
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" t="s">
         <v>24</v>
       </c>
-      <c r="D3">
-        <v>36</v>
-      </c>
-      <c r="E3">
-        <v>48</v>
-      </c>
-      <c r="F3">
-        <v>60</v>
-      </c>
-      <c r="G3">
-        <v>72</v>
-      </c>
-      <c r="H3">
-        <v>84</v>
-      </c>
-      <c r="I3">
-        <v>96</v>
-      </c>
-      <c r="J3">
-        <v>108</v>
-      </c>
-      <c r="K3">
-        <v>120</v>
+      <c r="H3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" t="s">
+        <v>28</v>
       </c>
       <c r="L3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="1">
+      <c r="A4" s="10">
         <v>32143</v>
       </c>
       <c r="B4">
@@ -605,7 +1169,8 @@
       <c r="K4">
         <v>6815646</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="19">
+        <f>(1+K17)</f>
         <v>1</v>
       </c>
       <c r="M4">
@@ -614,7 +1179,7 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="1">
+      <c r="A5" s="10">
         <v>32509</v>
       </c>
       <c r="B5">
@@ -654,7 +1219,7 @@
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A6" s="1">
+      <c r="A6" s="10">
         <v>32874</v>
       </c>
       <c r="B6">
@@ -691,7 +1256,7 @@
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A7" s="1">
+      <c r="A7" s="10">
         <v>33239</v>
       </c>
       <c r="B7">
@@ -725,7 +1290,7 @@
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A8" s="1">
+      <c r="A8" s="10">
         <v>33604</v>
       </c>
       <c r="B8">
@@ -756,7 +1321,7 @@
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A9" s="1">
+      <c r="A9" s="10">
         <v>33970</v>
       </c>
       <c r="B9">
@@ -784,7 +1349,7 @@
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A10" s="1">
+      <c r="A10" s="10">
         <v>34335</v>
       </c>
       <c r="B10">
@@ -809,7 +1374,7 @@
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A11" s="1">
+      <c r="A11" s="10">
         <v>34700</v>
       </c>
       <c r="B11">
@@ -831,7 +1396,7 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A12" s="1">
+      <c r="A12" s="10">
         <v>35065</v>
       </c>
       <c r="B12">
@@ -850,7 +1415,7 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A13" s="1">
+      <c r="A13" s="10">
         <v>35431</v>
       </c>
       <c r="B13">
@@ -896,10 +1461,13 @@
       <c r="J16" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K16" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="B17">
         <f>SUM(C4:C12)/SUM(B4:B12)</f>
@@ -937,17 +1505,20 @@
         <f>SUM(K4)/SUM(J4:J4)</f>
         <v>1.0010041403716861</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K17" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>2</v>
       </c>
       <c r="B18">
-        <f>B17</f>
+        <f>B17*(1+ $K$17)</f>
         <v>1.7959989238125871</v>
       </c>
       <c r="C18">
-        <f t="shared" ref="C18:J18" si="0">C17</f>
+        <f t="shared" ref="C18:J18" si="0">C17*(1+ $K$17)</f>
         <v>1.1938704351052822</v>
       </c>
       <c r="D18">
@@ -979,12 +1550,469 @@
         <v>1.0010041403716861</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" t="s">
         <v>21</v>
+      </c>
+      <c r="E23" t="s">
+        <v>22</v>
+      </c>
+      <c r="F23" t="s">
+        <v>23</v>
+      </c>
+      <c r="G23" t="s">
+        <v>24</v>
+      </c>
+      <c r="H23" t="s">
+        <v>25</v>
+      </c>
+      <c r="I23" t="s">
+        <v>26</v>
+      </c>
+      <c r="J23" t="s">
+        <v>27</v>
+      </c>
+      <c r="K23" t="s">
+        <v>28</v>
+      </c>
+      <c r="L23" t="s">
+        <v>17</v>
+      </c>
+      <c r="M23" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A24" s="10">
+        <v>32143</v>
+      </c>
+      <c r="B24">
+        <v>3092818</v>
+      </c>
+      <c r="C24">
+        <v>5942711</v>
+      </c>
+      <c r="D24">
+        <v>7239089</v>
+      </c>
+      <c r="E24">
+        <v>7930109</v>
+      </c>
+      <c r="F24">
+        <v>8318795</v>
+      </c>
+      <c r="G24">
+        <v>8518201</v>
+      </c>
+      <c r="H24">
+        <v>8610355</v>
+      </c>
+      <c r="I24">
+        <v>8655509</v>
+      </c>
+      <c r="J24">
+        <v>8682451</v>
+      </c>
+      <c r="K24">
+        <v>8690036</v>
+      </c>
+      <c r="L24" s="19">
+        <f>1+ K37</f>
+        <v>1</v>
+      </c>
+      <c r="M24">
+        <f>K24</f>
+        <v>8690036</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A25" s="10">
+        <v>32509</v>
+      </c>
+      <c r="B25">
+        <v>3556683</v>
+      </c>
+      <c r="C25">
+        <v>6753435</v>
+      </c>
+      <c r="D25">
+        <v>8219551</v>
+      </c>
+      <c r="E25">
+        <v>9018288</v>
+      </c>
+      <c r="F25">
+        <v>9441842</v>
+      </c>
+      <c r="G25">
+        <v>9647917</v>
+      </c>
+      <c r="H25">
+        <v>9753014</v>
+      </c>
+      <c r="I25">
+        <v>9800477</v>
+      </c>
+      <c r="J25">
+        <v>9823747</v>
+      </c>
+      <c r="L25">
+        <f>J38</f>
+        <v>1.0008736012446255</v>
+      </c>
+      <c r="M25">
+        <f>L25* J25</f>
+        <v>9832329.0376060866</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A26" s="10">
+        <v>32874</v>
+      </c>
+      <c r="B26">
+        <v>4015052</v>
+      </c>
+      <c r="C26">
+        <v>7478257</v>
+      </c>
+      <c r="D26">
+        <v>9094949</v>
+      </c>
+      <c r="E26">
+        <v>9945288</v>
+      </c>
+      <c r="F26">
+        <v>10371175</v>
+      </c>
+      <c r="G26">
+        <v>10575467</v>
+      </c>
+      <c r="H26">
+        <v>10671988</v>
+      </c>
+      <c r="I26">
+        <v>10728411</v>
+      </c>
+      <c r="L26">
+        <f>L25*I38</f>
+        <v>1.0035966129149689</v>
+      </c>
+      <c r="M26">
+        <f>L26*I26</f>
+        <v>10766996.941559695</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A27" s="10">
+        <v>33239</v>
+      </c>
+      <c r="B27">
+        <v>4065571</v>
+      </c>
+      <c r="C27">
+        <v>7564284</v>
+      </c>
+      <c r="D27">
+        <v>9161104</v>
+      </c>
+      <c r="E27">
+        <v>10006407</v>
+      </c>
+      <c r="F27">
+        <v>10419901</v>
+      </c>
+      <c r="G27">
+        <v>10612083</v>
+      </c>
+      <c r="H27">
+        <v>10713621</v>
+      </c>
+      <c r="L27">
+        <f>L26*H38</f>
+        <v>1.0087481266087337</v>
+      </c>
+      <c r="M27">
+        <f>L27*H27</f>
+        <v>10807345.112945989</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A28" s="10">
+        <v>33604</v>
+      </c>
+      <c r="B28">
+        <v>4551591</v>
+      </c>
+      <c r="C28">
+        <v>8344021</v>
+      </c>
+      <c r="D28">
+        <v>10047179</v>
+      </c>
+      <c r="E28">
+        <v>10901995</v>
+      </c>
+      <c r="F28">
+        <v>11336777</v>
+      </c>
+      <c r="G28">
+        <v>11555121</v>
+      </c>
+      <c r="L28">
+        <f>L27*G38</f>
+        <v>1.0188810631860739</v>
+      </c>
+      <c r="M28">
+        <f>L28 *G28</f>
+        <v>11773293.969723729</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A29" s="10">
+        <v>33970</v>
+      </c>
+      <c r="B29">
+        <v>5020277</v>
+      </c>
+      <c r="C29">
+        <v>9125734</v>
+      </c>
+      <c r="D29">
+        <v>10890282</v>
+      </c>
+      <c r="E29">
+        <v>11782219</v>
+      </c>
+      <c r="F29">
+        <v>12249826</v>
+      </c>
+      <c r="L29">
+        <f>L28*F38</f>
+        <v>1.0397188021091739</v>
+      </c>
+      <c r="M29">
+        <f>L29*F29</f>
+        <v>12736374.414765812</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A30" s="10">
+        <v>34335</v>
+      </c>
+      <c r="B30">
+        <v>5569355</v>
+      </c>
+      <c r="C30">
+        <v>9871002</v>
+      </c>
+      <c r="D30">
+        <v>11641397</v>
+      </c>
+      <c r="E30">
+        <v>12600432</v>
+      </c>
+      <c r="L30">
+        <f>L29*E38</f>
+        <v>1.0842851048160453</v>
+      </c>
+      <c r="M30">
+        <f>L30* E30</f>
+        <v>13662460.731847452</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A31" s="10">
+        <v>34700</v>
+      </c>
+      <c r="B31">
+        <v>5803124</v>
+      </c>
+      <c r="C31">
+        <v>10008734</v>
+      </c>
+      <c r="D31">
+        <v>11807279</v>
+      </c>
+      <c r="L31">
+        <f>L30*D38</f>
+        <v>1.1806402738699089</v>
+      </c>
+      <c r="M31">
+        <f>L31* D31</f>
+        <v>13940149.112218425</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A32" s="10">
+        <v>35065</v>
+      </c>
+      <c r="B32">
+        <v>5835368</v>
+      </c>
+      <c r="C32">
+        <v>9900842</v>
+      </c>
+      <c r="L32">
+        <f>L31*C38</f>
+        <v>1.4166779306783974</v>
+      </c>
+      <c r="M32">
+        <f>L32*C32</f>
+        <v>14026304.356533766</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A33" s="10">
+        <v>35431</v>
+      </c>
+      <c r="B33">
+        <v>5754249</v>
+      </c>
+      <c r="L33">
+        <f>L32*B38</f>
+        <v>2.5592797331061909</v>
+      </c>
+      <c r="M33">
+        <f>L33*B33</f>
+        <v>14726732.844946567</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A36" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B36" t="s">
+        <v>3</v>
+      </c>
+      <c r="C36" t="s">
+        <v>4</v>
+      </c>
+      <c r="D36" t="s">
+        <v>5</v>
+      </c>
+      <c r="E36" t="s">
+        <v>6</v>
+      </c>
+      <c r="F36" t="s">
+        <v>11</v>
+      </c>
+      <c r="G36" t="s">
+        <v>7</v>
+      </c>
+      <c r="H36" t="s">
+        <v>8</v>
+      </c>
+      <c r="I36" t="s">
+        <v>9</v>
+      </c>
+      <c r="J36" t="s">
+        <v>10</v>
+      </c>
+      <c r="K36" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>29</v>
+      </c>
+      <c r="B37">
+        <f>SUM(C24:C32)/ SUM(B24:B32)</f>
+        <v>1.8065360359504166</v>
+      </c>
+      <c r="C37">
+        <f>SUM(D24:D31)/SUM(C24:C31)</f>
+        <v>1.1999234331002475</v>
+      </c>
+      <c r="D37">
+        <f>SUM(E24:E30)/SUM(D24:D30)</f>
+        <v>1.0888651597498527</v>
+      </c>
+      <c r="E37">
+        <f>SUM(F24:F29)/SUM(E24:E29)</f>
+        <v>1.0428638037673881</v>
+      </c>
+      <c r="F37">
+        <f>SUM(G24:G28)/SUM(F24:F28)</f>
+        <v>1.0204515911385572</v>
+      </c>
+      <c r="G37">
+        <f>SUM(H24:H27)/SUM(G24:G27)</f>
+        <v>1.010045061110949</v>
+      </c>
+      <c r="H37">
+        <f>SUM(I24:I26)/SUM(H24:H26)</f>
+        <v>1.0051330520923163</v>
+      </c>
+      <c r="I37">
+        <f>SUM(J24:J25)/SUM(I24:I25)</f>
+        <v>1.0027206349202908</v>
+      </c>
+      <c r="J37">
+        <f>K24/J24</f>
+        <v>1.0008736012446255</v>
+      </c>
+      <c r="K37" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>2</v>
+      </c>
+      <c r="B38">
+        <f>B37 * (1+ $K$37)</f>
+        <v>1.8065360359504166</v>
+      </c>
+      <c r="C38">
+        <f t="shared" ref="C38:J38" si="1">C37 * (1+ $K$37)</f>
+        <v>1.1999234331002475</v>
+      </c>
+      <c r="D38">
+        <f t="shared" si="1"/>
+        <v>1.0888651597498527</v>
+      </c>
+      <c r="E38">
+        <f t="shared" si="1"/>
+        <v>1.0428638037673881</v>
+      </c>
+      <c r="F38">
+        <f t="shared" si="1"/>
+        <v>1.0204515911385572</v>
+      </c>
+      <c r="G38">
+        <f t="shared" si="1"/>
+        <v>1.010045061110949</v>
+      </c>
+      <c r="H38">
+        <f t="shared" si="1"/>
+        <v>1.0051330520923163</v>
+      </c>
+      <c r="I38">
+        <f t="shared" si="1"/>
+        <v>1.0027206349202908</v>
+      </c>
+      <c r="J38">
+        <f t="shared" si="1"/>
+        <v>1.0008736012446255</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="4">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+  </tableParts>
 </worksheet>
 </file>